--- a/Ke_hoach_nghien_cuu_CPA2_24_tuan.xlsx
+++ b/Ke_hoach_nghien_cuu_CPA2_24_tuan.xlsx
@@ -1748,10 +1748,14 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr"/>
+          <t>Hoàn thành</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>09/10/2026: OCR pipeline v1 (w15_ocr/) — Tesseract vie + OCR theo dải cột có whitelist; kiểm chéo mã∈CTĐT, TC, R-B02, tổng TC học kỳ, ĐTBCHK; confidence + ocr_raw mỗi fact. Ảnh tổng hợp 6 hồ sơ × 3 nhiễu: fact nhận đúng 783/784 (0,999), 0/18 kết luận sai, độ phủ chỉ 1/18 (còn lại UNKNOWN). Bảng điểm thật (không commit): trang 1 nhận 10/11, đúng 10/10. Review tìm 2 lỗi soundness (F/A không đơn điệu theo GPA; học lại) — đã sửa, có test. Phát hiện: KB Tuần 10 thế giới đóng cho xac_nhan_ky_luat_sach (FALSE thay vì UNKNOWN) → Tuần 16; bảng điểm thật ghi CC004 (miễn AV) và GDTC TC025–027, KB chỉ có TC100 → cần xác minh.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -2784,25 +2788,29 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>☑</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>☑</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>☑</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Đọc: không có phần đọc tài liệu OCR mới | Code: render_transcript.py, ocr_transcript.py, validate_ocr.py | Test: A chuẩn hoá, B 18 ca tổng hợp, C 3 ca tiêm lỗi, E 2 ca hồi quy, D bảng điểm thật | Artifact: Tuan15_OCR_Bang_Diem.md | Lỗi/phát hiện: F/A không đơn điệu; học lại; thế giới đóng ở KB; CC004; GDTC TC025–027; xoay -0,05° làm hỏng OCR</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">

--- a/Ke_hoach_nghien_cuu_CPA2_24_tuan.xlsx
+++ b/Ke_hoach_nghien_cuu_CPA2_24_tuan.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="22188" windowHeight="9000" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Kế hoạch 24 tuần" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Checklist tuần" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Tổng hợp giai đoạn" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kế hoạch 24 tuần" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist tuần" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tổng hợp giai đoạn" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Kế hoạch 24 tuần'!$A$1:$H$25</definedName>
@@ -1790,10 +1790,14 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr"/>
+          <t>Hoàn thành</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>14/10/2026: Abstention engine v1 (w16_abstention/). KB mở nhánh dữ kiện ngoài chưa khai báo (xac_nhan_ky_luat_sach, qua_thoi_gian_toi_da) → UNKNOWN thay vì FALSE/"chưa quá hạn" (sửa P15-2); missing evidence = chỉ dữ kiện QUYẾT ĐỊNH + câu hỏi + nguồn + kết luận theo từng giá trị; UNKNOWN → không kết luận, không theo đa số. validate_abstention 28/28 (tự soạn; 14 fail với luật cũ), mọi tuần 5–16 ĐẠT. LƯU Ý: P16-2 tot_nghiep chưa phụ thuộc điều kiện thời gian (R-Formal Đ32 k1 vs Đ5) — cần quyết định diễn giải; tc_cong_nhan vẫn thế giới đóng.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -2823,25 +2827,29 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>☑</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>☑</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>☑</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr"/>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Đọc: không có phần đọc tài liệu ba trị/abstention mới | Code: abstention.py, graduation_solver.lp mục 0, loader w7/w11/w12 | Test: validate_abstention 28/28 (A9 B10 C5 D4), w10 B6 đổi FALSE→UNKNOWN + B6b | Artifact: Tuan16_Abstention_Engine.md | Lỗi/phát hiện: khai_bao tự triệt nhánh (P16-1); tot_nghiep bỏ qua thời gian (P16-2, chưa sửa); tc_cong_nhan thế giới đóng; đường dẫn D:/ &amp; font Windows; g10 nhiều giá trị/mô hình</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">

--- a/Ke_hoach_nghien_cuu_CPA2_24_tuan.xlsx
+++ b/Ke_hoach_nghien_cuu_CPA2_24_tuan.xlsx
@@ -1795,7 +1795,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14/10/2026: Abstention engine v1 (w16_abstention/). KB mở nhánh dữ kiện ngoài chưa khai báo (xac_nhan_ky_luat_sach, qua_thoi_gian_toi_da) → UNKNOWN thay vì FALSE/"chưa quá hạn" (sửa P15-2); missing evidence = chỉ dữ kiện QUYẾT ĐỊNH + câu hỏi + nguồn + kết luận theo từng giá trị; UNKNOWN → không kết luận, không theo đa số. validate_abstention 28/28 (tự soạn; 14 fail với luật cũ), mọi tuần 5–16 ĐẠT. LƯU Ý: P16-2 tot_nghiep chưa phụ thuộc điều kiện thời gian (R-Formal Đ32 k1 vs Đ5) — cần quyết định diễn giải; tc_cong_nhan vẫn thế giới đóng.</t>
+          <t>14/10/2026: Abstention engine v1 (w16_abstention/). KB mở nhánh dữ kiện ngoài chưa khai báo (xac_nhan_ky_luat_sach, qua_thoi_gian_toi_da) → UNKNOWN thay vì FALSE/"chưa quá hạn" (sửa P15-2); missing evidence = chỉ dữ kiện QUYẾT ĐỊNH + câu hỏi + nguồn + kết luận theo từng giá trị; UNKNOWN → không kết luận, không theo đa số. validate_abstention 30/30 (tự soạn; 14 fail với luật cũ), mọi tuần 5–16 ĐẠT. P16-2 đã sửa 17/10/2026 (chọn cách đọc b): quá thời gian tối đa (Đ5, CTĐT 4,5 năm → 9 năm) thì không tốt nghiệp — R-Formal v1.7 + graduation_solver, 5 ca hồi quy fail với luật cũ. LƯU Ý: tc_cong_nhan vẫn thế giới đóng; học phí ×1,5 sau thời gian thiết kế chưa có văn bản nguồn (không có trong QĐ3266/QĐ5339) → chưa hình thức hoá.</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Đọc: không có phần đọc tài liệu ba trị/abstention mới | Code: abstention.py, graduation_solver.lp mục 0, loader w7/w11/w12 | Test: validate_abstention 28/28 (A9 B10 C5 D4), w10 B6 đổi FALSE→UNKNOWN + B6b | Artifact: Tuan16_Abstention_Engine.md | Lỗi/phát hiện: khai_bao tự triệt nhánh (P16-1); tot_nghiep bỏ qua thời gian (P16-2, chưa sửa); tc_cong_nhan thế giới đóng; đường dẫn D:/ &amp; font Windows; g10 nhiều giá trị/mô hình</t>
+          <t>Đọc: không có phần đọc tài liệu ba trị/abstention mới | Code: abstention.py, graduation_solver.lp mục 0, loader w7/w11/w12 | Test: validate_abstention 30/30 (A11 B10 C5 D4); hồi quy P16-2 w5 C9b/c, w10 B7b–d, w10 B6 đổi FALSE→UNKNOWN + B6b | Artifact: Tuan16_Abstention_Engine.md | Lỗi/phát hiện: khai_bao tự triệt nhánh (P16-1); tot_nghiep bỏ qua thời gian (P16-2, đã sửa v1.7); tc_cong_nhan thế giới đóng; đường dẫn D:/ &amp; font Windows; g10 nhiều giá trị/mô hình</t>
         </is>
       </c>
     </row>

--- a/Ke_hoach_nghien_cuu_CPA2_24_tuan.xlsx
+++ b/Ke_hoach_nghien_cuu_CPA2_24_tuan.xlsx
@@ -1832,10 +1832,14 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr"/>
+          <t>Hoàn thành</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>17/10/2026: Adversarial set v1 (w17_adversarial/) — 80 ca chấm điểm (thiếu dữ liệu 17, sát ngưỡng 24, bẫy quy chế 15, hồ sơ lỗi 6, OCR sai mức tài liệu 18) + 5 ca không chấm; gold viết tay kèm nguồn điều/khoản/trang, ĐÓNG BĂNG ở commit 200b860 trước khi chạy; oracle Python độc lập kiểm 29 tiền đề; dev/test phân tầng. CPA² test (37 ca): Soundness 91,9%, Coverage 78,4%, SelAcc 89,7%, từ chối thừa 0. LƯU Ý: hồ sơ mâu thuẫn 0/6 sound (P17-1, loader tin mọi bản ghi); lỗi OCR nhất quán 2/2 trái sự thật (P17-2); đơn vị HK trong trần thời gian sai (Đ6: 3 HK/năm, P17-3); gold tự soạn, chưa đo κ.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -2862,25 +2866,29 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>☑</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>☑</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>☑</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr"/>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Đọc: không có phần đọc tài liệu adversarial evaluation mới (chỉ đọc lại QĐ3266/QĐ5339 để lấy nguồn gold) | Code: build_adversarial.py, oracle.py, dau_vao.py, run_adversarial.py, validate_adversarial.py | Test/Dataset: 80 ca (dev 41/test 39), gold đóng băng 200b860 | Artifact: adversarial_set.json + Tuan17_Adversarial_Set.md | Lỗi/phát hiện: P17-1 hồ sơ mâu thuẫn 0/6; P17-2 OCR nhất quán 2/2; P17-3 1 HK = 1/3 năm (Đ6 k1); errata E17-1…5</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">

--- a/Ke_hoach_nghien_cuu_CPA2_24_tuan.xlsx
+++ b/Ke_hoach_nghien_cuu_CPA2_24_tuan.xlsx
@@ -1837,7 +1837,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17/10/2026: Adversarial set v1 (w17_adversarial/) — 80 ca chấm điểm (thiếu dữ liệu 17, sát ngưỡng 24, bẫy quy chế 15, hồ sơ lỗi 6, OCR sai mức tài liệu 18) + 5 ca không chấm; gold viết tay kèm nguồn điều/khoản/trang, ĐÓNG BĂNG ở commit 200b860 trước khi chạy; oracle Python độc lập kiểm 29 tiền đề; dev/test phân tầng. CPA² test (37 ca): Soundness 91,9%, Coverage 78,4%, SelAcc 89,7%, từ chối thừa 0. LƯU Ý: hồ sơ mâu thuẫn 0/6 sound (P17-1, loader tin mọi bản ghi); lỗi OCR nhất quán 2/2 trái sự thật (P17-2); đơn vị HK trong trần thời gian sai (Đ6: 3 HK/năm, P17-3); gold tự soạn, chưa đo κ.</t>
+          <t>17/10/2026: Adversarial set v1 (w17_adversarial/) — 80 ca chấm điểm (thiếu dữ liệu 17, sát ngưỡng 24, bẫy quy chế 15, hồ sơ lỗi 6, OCR sai mức tài liệu 18) + 5 ca không chấm; gold viết tay kèm nguồn điều/khoản/trang, ĐÓNG BĂNG ở commit 200b860 trước khi chạy; oracle Python độc lập kiểm 29 tiền đề; dev/test phân tầng. CPA² test (37 ca): Soundness 91,9%, Coverage 78,4%, SelAcc 89,7%, từ chối thừa 0. SỬA 18/10/2026: P17-1 rà soát hồ sơ mâu thuẫn (abstention.ra_soat), P17-2 OCR (ĐTBCHK không đọc được; mã bắt buộc đọc nhầm), P17-3 R-Formal v1.8 trần theo HK (Đ6 k1: 3 HK/năm). Chạy lại: dev/test 100% sound, 0/2 rủi ro OCR ẩn — NHƯNG test đã nhiễm (sửa sau khi thấy ca test) → cần bộ test mới ở Tuần 20. LƯU Ý: số chính thức T17 giữ nguyên; gold tự soạn, chưa đo κ; 3 bản loader chưa gộp.</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Đọc: không có phần đọc tài liệu adversarial evaluation mới (chỉ đọc lại QĐ3266/QĐ5339 để lấy nguồn gold) | Code: build_adversarial.py, oracle.py, dau_vao.py, run_adversarial.py, validate_adversarial.py | Test/Dataset: 80 ca (dev 41/test 39), gold đóng băng 200b860 | Artifact: adversarial_set.json + Tuan17_Adversarial_Set.md | Lỗi/phát hiện: P17-1 hồ sơ mâu thuẫn 0/6; P17-2 OCR nhất quán 2/2; P17-3 1 HK = 1/3 năm (Đ6 k1); errata E17-1…5</t>
+          <t>Đọc: không có phần đọc tài liệu adversarial evaluation mới (chỉ đọc lại QĐ3266/QĐ5339 để lấy nguồn gold) | Code: build_adversarial.py, oracle.py, dau_vao.py, run_adversarial.py, validate_adversarial.py | Test/Dataset: 80 ca (dev 41/test 39), gold đóng băng 200b860 | Artifact: adversarial_set.json + Tuan17_Adversarial_Set.md | Lỗi/phát hiện: P17-1 hồ sơ mâu thuẫn 0/6; P17-2 OCR nhất quán 2/2; P17-3 1 HK = 1/3 năm (Đ6 k1); errata E17-1…5 | Sau T17: sửa P17-1/2/3 (TDD: w16 E1–E12, w15 F1–F4, w5 C16b, w10 B7e)</t>
         </is>
       </c>
     </row>

--- a/Ke_hoach_nghien_cuu_CPA2_24_tuan.xlsx
+++ b/Ke_hoach_nghien_cuu_CPA2_24_tuan.xlsx
@@ -2886,7 +2886,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Đọc: không có phần đọc tài liệu adversarial evaluation mới (chỉ đọc lại QĐ3266/QĐ5339 để lấy nguồn gold) | Code: build_adversarial.py, oracle.py, dau_vao.py, run_adversarial.py, validate_adversarial.py | Test/Dataset: 80 ca (dev 41/test 39), gold đóng băng 200b860 | Artifact: adversarial_set.json + Tuan17_Adversarial_Set.md | Lỗi/phát hiện: P17-1 hồ sơ mâu thuẫn 0/6; P17-2 OCR nhất quán 2/2; P17-3 1 HK = 1/3 năm (Đ6 k1); errata E17-1…5 | Sau T17: sửa P17-1/2/3 (TDD: w16 E1–E12, w15 F1–F4, w5 C16b, w10 B7e)</t>
+          <t>Đọc: không có phần đọc tài liệu adversarial evaluation mới (chỉ đọc lại QĐ3266/QĐ5339 để lấy nguồn gold) | Code: build_adversarial.py, oracle.py, dau_vao.py, run_adversarial.py, validate_adversarial.py | Test/Dataset: 80 ca (dev 41/test 39), gold đóng băng 200b860 | Artifact: adversarial_set.json + Tuan17_Adversarial_Set.md | Lỗi/phát hiện: P17-1 hồ sơ mâu thuẫn 0/6; P17-2 OCR nhất quán 2/2; P17-3 1 HK = 1/3 năm (Đ6 k1); errata E17-1…5 | Sau T17: sửa P17-1/2/3 (TDD: w16 E1–E12, w15 F1–F4, w5 C16b, w10 B7e) | Hoàn tất trước T18: loader dùng chung w7/loader.py (L1–L3), w15 tự dò font/Tesseract, sổ Viec_ton_dong.md (22 mục cũ đã tích kèm con trỏ)</t>
         </is>
       </c>
     </row>

--- a/Ke_hoach_nghien_cuu_CPA2_24_tuan.xlsx
+++ b/Ke_hoach_nghien_cuu_CPA2_24_tuan.xlsx
@@ -1874,10 +1874,14 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr"/>
+          <t>Hoàn thành</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>18/10/2026: Eligibility module v1 (w18_eligibility/) — ELIGIBLE/NOT_ELIGIBLE/UNKNOWN (+DA_HOAN_THANH, MAU_THUAN) cho LVTN, TLTN, niên luận, niên luận cơ sở, thực tập, tích lũy TC thay LVTN (Đ31 k3), HP thay thế (QĐ5339 Đ3 k9); lý do (thiếu TC/tiên quyết) + chứng chỉ điều/khoản + câu hỏi bổ sung. validate_eligibility 36/36 (tự soạn), mọi tuần 5–18 ĐẠT. Phát hiện P18-1: prototype luôn FALSE cho "đủ điều kiện làm luận văn" (claim du_dk_tc không đối số) — đã sửa. LƯU Ý: điều kiện nhận đề tài LVTN/TLTN do đơn vị đào tạo quy định (Đ31, R-F04) — chưa có văn bản → chỉ nhận kết quả xét (hinh_thuc_cuoi_khoa), thiếu → UNKNOWN.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -2901,25 +2905,29 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>☑</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>☑</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>☑</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr"/>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Đọc: không có phần đọc tài liệu mới (chỉ đối chiếu QĐ3266 Đ31, CTĐT) | Code: eligibility.lp, eligibility.py, prototype.answer_eligibility, loader hinh_thuc_cuoi_khoa | Test: validate_eligibility 36/36 | Artifact: Tuan18_Eligibility.md | Lỗi/phát hiện: P18-1 claim du_dk_tc không đối số → luôn FALSE; P18-2 đủ TC ≠ đủ ĐK (R-F04); P18-3 đã xong hình thức khác</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">

--- a/Ke_hoach_nghien_cuu_CPA2_24_tuan.xlsx
+++ b/Ke_hoach_nghien_cuu_CPA2_24_tuan.xlsx
@@ -1879,7 +1879,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026: Eligibility module v1 (w18_eligibility/) — ELIGIBLE/NOT_ELIGIBLE/UNKNOWN (+DA_HOAN_THANH, MAU_THUAN) cho LVTN, TLTN, niên luận, niên luận cơ sở, thực tập, tích lũy TC thay LVTN (Đ31 k3), HP thay thế (QĐ5339 Đ3 k9); lý do (thiếu TC/tiên quyết) + chứng chỉ điều/khoản + câu hỏi bổ sung. validate_eligibility 36/36 (tự soạn), mọi tuần 5–18 ĐẠT. Phát hiện P18-1: prototype luôn FALSE cho "đủ điều kiện làm luận văn" (claim du_dk_tc không đối số) — đã sửa. LƯU Ý: điều kiện nhận đề tài LVTN/TLTN do đơn vị đào tạo quy định (Đ31, R-F04) — chưa có văn bản → chỉ nhận kết quả xét (hinh_thuc_cuoi_khoa), thiếu → UNKNOWN.</t>
+          <t>18/10/2026: Eligibility module v1 (w18_eligibility/) — ELIGIBLE/NOT_ELIGIBLE/UNKNOWN (+DA_HOAN_THANH, MAU_THUAN) cho LVTN, TLTN, niên luận, niên luận cơ sở, thực tập, tích lũy TC thay LVTN (Đ31 k3), HP thay thế (QĐ5339 Đ3 k9); lý do (thiếu TC/tiên quyết) + chứng chỉ điều/khoản + câu hỏi bổ sung. validate_eligibility 36/36 (tự soạn), mọi tuần 5–18 ĐẠT. Phát hiện P18-1: prototype luôn FALSE cho "đủ điều kiện làm luận văn" (claim du_dk_tc không đối số) — đã sửa. CẬP NHẬT QD-12 (Loi xác nhận 18/10/2026): điều kiện nhận đề tài LVTN/TLTN CHỈ là ngưỡng TC → đủ 120 TC = ELIGIBLE; R-F04 N→F; R-Formal F=59 P=8 N=4, Formalization 83,1%, Executable 60,6%. LƯU Ý: xác nhận ngoài văn bản — nên có email/biên bản.</t>
         </is>
       </c>
     </row>

--- a/Ke_hoach_nghien_cuu_CPA2_24_tuan.xlsx
+++ b/Ke_hoach_nghien_cuu_CPA2_24_tuan.xlsx
@@ -1916,10 +1916,14 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr"/>
+          <t>Hoàn thành</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>18/10/2026: Recommendation v1 (w19_recommendation/) — đề xuất đăng ký 1 HK (hk 1/2/3): ứng viên hợp lệ trên MỌI thế giới (du_dk_dang_ky TRUE, chưa tích lũy, mở HK, cần cho CTĐT; nhóm một nhánh), clingo tối ưu ≤20 TC (R-C01) + ưu tiên CHÍNH SÁCH (bắt buộc → mở khóa → song hành → nhóm → TC); UNKNOWN → cần xác minh; hình thức tốt nghiệp qua Eligibility; xin miễn (nộp đơn, QD-11); thay thế (R-M13). validate_recommendation 34/34 (tự soạn), bất biến kiểm lại độc lập 21 lần đề xuất, mọi tuần 5–19 ĐẠT. QD-13 (Loi 18/10/2026): song hành học trước/cùng/sau — KHÁC câu chữ Đ7 k5 → KB giữ R-A04, chỉ là lời khuyên. Phát hiện P19-1 (đủ ĐK xin miễn ≠ cần), P19-2 (AV tăng cường trước căn bản), P19-3 (parser kì/kỳ, HK4, NFD). Hạn chế: chỉ 1 HK, chưa lịch học.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2940,25 +2944,29 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>☑</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>☑</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>☑</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr"/>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Đọc: không có phần đọc tài liệu mới | Code: recommendation.py, recommendation.lp, prototype.answer_recommendation + parser de_xuat | Test: validate_recommendation 34/34 | Artifact: Tuan19_Recommendation.md | Lỗi/phát hiện: P19-1 đủ ĐK xin miễn ≠ cần; P19-2 ưu tiên TC chọn AV tăng cường trước căn bản; P19-3 parser học kỳ/ý định</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">

--- a/Ke_hoach_nghien_cuu_CPA2_24_tuan.xlsx
+++ b/Ke_hoach_nghien_cuu_CPA2_24_tuan.xlsx
@@ -1921,7 +1921,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026: Recommendation v1 (w19_recommendation/) — đề xuất đăng ký 1 HK (hk 1/2/3): ứng viên hợp lệ trên MỌI thế giới (du_dk_dang_ky TRUE, chưa tích lũy, mở HK, cần cho CTĐT; nhóm một nhánh), clingo tối ưu ≤20 TC (R-C01) + ưu tiên CHÍNH SÁCH (bắt buộc → mở khóa → song hành → nhóm → TC); UNKNOWN → cần xác minh; hình thức tốt nghiệp qua Eligibility; xin miễn (nộp đơn, QD-11); thay thế (R-M13). validate_recommendation 34/34 (tự soạn), bất biến kiểm lại độc lập 21 lần đề xuất, mọi tuần 5–19 ĐẠT. QD-13 (Loi 18/10/2026): song hành học trước/cùng/sau — KHÁC câu chữ Đ7 k5 → KB giữ R-A04, chỉ là lời khuyên. Phát hiện P19-1 (đủ ĐK xin miễn ≠ cần), P19-2 (AV tăng cường trước căn bản), P19-3 (parser kì/kỳ, HK4, NFD). Hạn chế: chỉ 1 HK, chưa lịch học.</t>
+          <t>18/10/2026: Recommendation v1 (w19_recommendation/) — đề xuất đăng ký 1 HK (hk 1/2/3): ứng viên hợp lệ trên MỌI thế giới (du_dk_dang_ky TRUE, chưa tích lũy, mở HK, cần cho CTĐT; nhóm một nhánh), clingo tối ưu ≤20 TC (R-C01) + ưu tiên CHÍNH SÁCH (bắt buộc → mở khóa → nhóm → TC); UNKNOWN → cần xác minh; hình thức tốt nghiệp qua Eligibility; xin miễn (nộp đơn, QD-11); thay thế (R-M13). validate_recommendation 39/39 (tự soạn), bất biến kiểm lại độc lập 21 lần đề xuất, mọi tuần 5–19 ĐẠT. CẬP NHẬT: QD-13 RÚT LẠI sau khi đối chiếu PDF gốc — song hành theo đúng QĐ3266 Đ7 k5 (học trước/cùng lúc; đã học kể cả F, W không tính) → ràng buộc cứng. Trang 20 QĐ3266 (OCR trắng) đã chép tay từ PDF gốc. Phát hiện P19-1 (đủ ĐK xin miễn ≠ cần), P19-2 (AV tăng cường trước căn bản), P19-3 (parser kì/kỳ, HK4, NFD). Hạn chế: chỉ 1 HK, chưa lịch học.</t>
         </is>
       </c>
     </row>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Đọc: không có phần đọc tài liệu mới | Code: recommendation.py, recommendation.lp, prototype.answer_recommendation + parser de_xuat | Test: validate_recommendation 34/34 | Artifact: Tuan19_Recommendation.md | Lỗi/phát hiện: P19-1 đủ ĐK xin miễn ≠ cần; P19-2 ưu tiên TC chọn AV tăng cường trước căn bản; P19-3 parser học kỳ/ý định</t>
+          <t>Đọc: không có phần đọc tài liệu mới | Code: recommendation.py, recommendation.lp, prototype.answer_recommendation + parser de_xuat | Test: validate_recommendation 39/39 | Artifact: Tuan19_Recommendation.md | Lỗi/phát hiện: P19-1 đủ ĐK xin miễn ≠ cần; P19-2 ưu tiên TC chọn AV tăng cường trước căn bản; P19-3 parser học kỳ/ý định</t>
         </is>
       </c>
     </row>

--- a/Ke_hoach_nghien_cuu_CPA2_24_tuan.xlsx
+++ b/Ke_hoach_nghien_cuu_CPA2_24_tuan.xlsx
@@ -1921,7 +1921,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026: Recommendation v1 (w19_recommendation/) — đề xuất đăng ký 1 HK (hk 1/2/3): ứng viên hợp lệ trên MỌI thế giới (du_dk_dang_ky TRUE, chưa tích lũy, mở HK, cần cho CTĐT; nhóm một nhánh), clingo tối ưu ≤20 TC (R-C01) + ưu tiên CHÍNH SÁCH (bắt buộc → mở khóa → nhóm → TC); UNKNOWN → cần xác minh; hình thức tốt nghiệp qua Eligibility; xin miễn (nộp đơn, QD-11); thay thế (R-M13). validate_recommendation 39/39 (tự soạn), bất biến kiểm lại độc lập 21 lần đề xuất, mọi tuần 5–19 ĐẠT. CẬP NHẬT: QD-13 RÚT LẠI sau khi đối chiếu PDF gốc — song hành theo đúng QĐ3266 Đ7 k5 (học trước/cùng lúc; đã học kể cả F, W không tính) → ràng buộc cứng. Trang 20 QĐ3266 (OCR trắng) đã chép tay từ PDF gốc. Phát hiện P19-1 (đủ ĐK xin miễn ≠ cần), P19-2 (AV tăng cường trước căn bản), P19-3 (parser kì/kỳ, HK4, NFD). Hạn chế: chỉ 1 HK, chưa lịch học.</t>
+          <t>18/10/2026: Recommendation v1 (w19_recommendation/) — đề xuất đăng ký 1 HK (hk 1/2/3): ứng viên hợp lệ trên MỌI thế giới (du_dk_dang_ky TRUE, chưa tích lũy, mở HK, cần cho CTĐT; nhóm một nhánh), clingo tối ưu ≤20 TC (R-C01) + ưu tiên CHÍNH SÁCH (bắt buộc → mở khóa → nhóm → TC); UNKNOWN → cần xác minh; hình thức tốt nghiệp qua Eligibility; xin miễn (nộp đơn, QD-11); thay thế (R-M13). validate_recommendation 39/39 (tự soạn), bất biến kiểm lại độc lập 21 lần đề xuất, mọi tuần 5–19 ĐẠT. CẬP NHẬT: QD-13 RÚT LẠI sau khi đối chiếu PDF gốc — song hành theo đúng QĐ3266 Đ7 k5 (học trước/cùng lúc; đã học kể cả F, W không tính) → ràng buộc cứng. Trang 20 QĐ3266 (OCR trắng) đã chép tay từ PDF gốc. Phát hiện P19-1 (đủ ĐK xin miễn ≠ cần), P19-2 (AV tăng cường trước căn bản), P19-3 (parser kì/kỳ, HK4, NFD). Hạn chế: chỉ 1 HK, chưa lịch học. | SAU TUẦN 19: R-Formal v1.9 — song hành khi hỏi đăng ký MỘT HP: duoc_dang_ky = tiên quyết + song hành (bắc cầu; chưa học → phải học cùng kỳ; HP song hành không đăng ký được → chặn). P19-4: câu 'đăng ký CT180 được chưa' trước đây bị trả lời thành tot_nghiep (khoá parser viết HOA không khớp) — đã sửa, kèm ca hồi quy.</t>
         </is>
       </c>
     </row>

--- a/Ke_hoach_nghien_cuu_CPA2_24_tuan.xlsx
+++ b/Ke_hoach_nghien_cuu_CPA2_24_tuan.xlsx
@@ -1958,10 +1958,14 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr"/>
+          <t>Hoàn thành một phần</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>18/10/2026: w20_benchmark/ — G-Truth v1 115 ca (114 chấm) + OCR-Noise v1 40 ca, gold viết tay + nguồn + oracle độc lập (41 tiền đề), loai_gold quy_che/thiet_ke, soát độc lập (không chạy hệ thống) rồi ĐÓNG BĂNG 312b7ff trước lần chạy đầu; không trùng w17; dev/test. Đầu vào baseline trung lập (baseline_dev/test.jsonl). Q-Real: pipeline nhập/ẩn danh xong, CHƯA ĐẠT 0/400 (chờ câu hỏi thật). Chạy dev: G-Truth Soundness 89,7% (6 unsound: P20-1 hạng tốt nghiệp mốc nguyên, P20-2/3 parser), OCR-Noise 100% sound, coverage 25% (M2 từ chối thừa). validate_benchmark ĐẠT; mọi tuần 5–20 ĐẠT. Test → Tuần 22.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2979,25 +2983,29 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>☑</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>☑</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>☑</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr"/>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Đọc: không | Code: build_benchmark.py, validate_benchmark.py, run_cpa2.py, baseline.py, nhap_qreal.py | Test: validate_benchmark B1–B9 ĐẠT | Artifact: Tuan20_Benchmark.md, gtruth.json, ocr_noise.json | Lỗi/phát hiện: P20-1 hạng TN mốc nguyên; P20-2 ngoài phạm vi → tot_nghiep; P20-3 đăng ký niên luận; P20-4 OCR M2 từ chối thừa; Q-Real 0/400 chưa đạt</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">

--- a/Ke_hoach_nghien_cuu_CPA2_24_tuan.xlsx
+++ b/Ke_hoach_nghien_cuu_CPA2_24_tuan.xlsx
@@ -1963,7 +1963,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026: w20_benchmark/ — G-Truth v1 115 ca (114 chấm) + OCR-Noise v1 40 ca, gold viết tay + nguồn + oracle độc lập (41 tiền đề), loai_gold quy_che/thiet_ke, soát độc lập (không chạy hệ thống) rồi ĐÓNG BĂNG 312b7ff trước lần chạy đầu; không trùng w17; dev/test. Đầu vào baseline trung lập (baseline_dev/test.jsonl). Q-Real: pipeline nhập/ẩn danh xong, CHƯA ĐẠT 0/400 (chờ câu hỏi thật). Chạy dev: G-Truth Soundness 89,7% (6 unsound: P20-1 hạng tốt nghiệp mốc nguyên, P20-2/3 parser), OCR-Noise 100% sound, coverage 25% (M2 từ chối thừa). validate_benchmark ĐẠT; mọi tuần 5–20 ĐẠT. Test → Tuần 22.</t>
+          <t>18/10/2026: w20_benchmark/ — G-Truth v1 115 ca (114 chấm) + OCR-Noise v1 40 ca, gold viết tay + nguồn + oracle độc lập (41 tiền đề), loai_gold quy_che/thiet_ke, soát độc lập (không chạy hệ thống) rồi ĐÓNG BĂNG 312b7ff trước lần chạy đầu; không trùng w17; dev/test. Đầu vào baseline trung lập (baseline_dev/test.jsonl). Q-Real: pipeline nhập/ẩn danh xong, CHƯA ĐẠT 0/400 (chờ câu hỏi thật). Chạy dev: G-Truth Soundness 89,7% (6 unsound: P20-1 hạng tốt nghiệp mốc nguyên, P20-2/3 parser), OCR-Noise 100% sound, coverage 25% (M2 từ chối thừa). validate_benchmark ĐẠT. SỬA P20-1 (R-Formal v1.10: hạng so hữu tỉ theo cận dưới, QD-14 không làm tròn ĐTBCTL), P20-2 (parser không mặc định tot_nghiep → UNKNOWN 'chưa hỗ trợ'), P20-3 (đăng ký có tên HP chen giữa) — ca hồi quy fail với luật cũ; G-Truth dev sau sửa 100% sound (dev đã nhìn thấy; số chính thức = test, Tuần 22). Còn: Q-Real 0/400, P20-4. Mọi tuần 5–20 ĐẠT.</t>
         </is>
       </c>
     </row>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Đọc: không | Code: build_benchmark.py, validate_benchmark.py, run_cpa2.py, baseline.py, nhap_qreal.py | Test: validate_benchmark B1–B9 ĐẠT | Artifact: Tuan20_Benchmark.md, gtruth.json, ocr_noise.json | Lỗi/phát hiện: P20-1 hạng TN mốc nguyên; P20-2 ngoài phạm vi → tot_nghiep; P20-3 đăng ký niên luận; P20-4 OCR M2 từ chối thừa; Q-Real 0/400 chưa đạt</t>
+          <t>Đọc: không | Code: build_benchmark.py, validate_benchmark.py, run_cpa2.py, baseline.py, nhap_qreal.py | Test: validate_benchmark B1–B9 ĐẠT | Artifact: Tuan20_Benchmark.md, gtruth.json, ocr_noise.json | Lỗi/phát hiện: P20-1 hạng TN mốc nguyên; P20-2 ngoài phạm vi → tot_nghiep; P20-3 đăng ký niên luận; P20-4 OCR M2 từ chối thừa; Q-Real 0/400 chưa đạt | Sửa: P20-1 (v1.10, QD-14), P20-2, P20-3 — rformal C42–C46, integration E10–E16</t>
         </is>
       </c>
     </row>

--- a/Ke_hoach_nghien_cuu_CPA2_24_tuan.xlsx
+++ b/Ke_hoach_nghien_cuu_CPA2_24_tuan.xlsx
@@ -1963,7 +1963,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026: w20_benchmark/ — G-Truth v1 115 ca (114 chấm) + OCR-Noise v1 40 ca, gold viết tay + nguồn + oracle độc lập (41 tiền đề), loai_gold quy_che/thiet_ke, soát độc lập (không chạy hệ thống) rồi ĐÓNG BĂNG 312b7ff trước lần chạy đầu; không trùng w17; dev/test. Đầu vào baseline trung lập (baseline_dev/test.jsonl). Q-Real: pipeline nhập/ẩn danh xong, CHƯA ĐẠT 0/400 (chờ câu hỏi thật). Chạy dev: G-Truth Soundness 89,7% (6 unsound: P20-1 hạng tốt nghiệp mốc nguyên, P20-2/3 parser), OCR-Noise 100% sound, coverage 25% (M2 từ chối thừa). validate_benchmark ĐẠT. SỬA P20-1 (R-Formal v1.10: hạng so hữu tỉ theo cận dưới, QD-14 không làm tròn ĐTBCTL), P20-2 (parser không mặc định tot_nghiep → UNKNOWN 'chưa hỗ trợ'), P20-3 (đăng ký có tên HP chen giữa) — ca hồi quy fail với luật cũ; G-Truth dev sau sửa 100% sound (dev đã nhìn thấy; số chính thức = test, Tuần 22). Còn: Q-Real 0/400, P20-4. Mọi tuần 5–20 ĐẠT.</t>
+          <t>18/10/2026: w20_benchmark/ — G-Truth v1 115 ca (114 chấm) + OCR-Noise v1 40 ca, gold viết tay + nguồn + oracle độc lập (41 tiền đề), loai_gold quy_che/thiet_ke, soát độc lập (không chạy hệ thống) rồi ĐÓNG BĂNG 312b7ff trước lần chạy đầu; không trùng w17; dev/test. Đầu vào baseline trung lập (baseline_dev/test.jsonl). Q-Real: pipeline nhập/ẩn danh xong, CHƯA ĐẠT 0/400 (chờ câu hỏi thật). Chạy dev: G-Truth Soundness 89,7% (6 unsound: P20-1 hạng tốt nghiệp mốc nguyên, P20-2/3 parser), OCR-Noise 100% sound, coverage 25% (M2 từ chối thừa). validate_benchmark ĐẠT. SỬA P20-1 (R-Formal v1.10: hạng so hữu tỉ theo cận dưới, QD-14 không làm tròn ĐTBCTL), P20-2 (parser không mặc định tot_nghiep → UNKNOWN 'chưa hỗ trợ'), P20-3 (đăng ký có tên HP chen giữa) — ca hồi quy fail với luật cũ; G-Truth dev sau sửa 100% sound (dev đã nhìn thấy; số chính thức = test, Tuần 22). Còn: Q-Real 0/400, P20-4. Mọi tuần 5–20 ĐẠT. | Q-Noise v1 (TỔNG HỢP, không thay Q-Real): 240 câu = 48 câu G-Truth × 5 kiểu gõ (gốc/bỏ dấu/viết tắt/gõ vội/bỏ dấu+viết tắt), gold kế thừa + ý định gán tay, đóng băng 5d8601c; dev: Sound 96,9%, Coverage 38,5% (V2/V4 0%), phát hiện P20-5 (4 unsound: luan van không dấu → tot_nghiep), chưa sửa.</t>
         </is>
       </c>
     </row>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Đọc: không | Code: build_benchmark.py, validate_benchmark.py, run_cpa2.py, baseline.py, nhap_qreal.py | Test: validate_benchmark B1–B9 ĐẠT | Artifact: Tuan20_Benchmark.md, gtruth.json, ocr_noise.json | Lỗi/phát hiện: P20-1 hạng TN mốc nguyên; P20-2 ngoài phạm vi → tot_nghiep; P20-3 đăng ký niên luận; P20-4 OCR M2 từ chối thừa; Q-Real 0/400 chưa đạt | Sửa: P20-1 (v1.10, QD-14), P20-2, P20-3 — rformal C42–C46, integration E10–E16</t>
+          <t>Đọc: không | Code: build_benchmark.py, validate_benchmark.py, run_cpa2.py, baseline.py, nhap_qreal.py | Test: validate_benchmark B1–B10 ĐẠT | Artifact: Tuan20_Benchmark.md, gtruth.json, ocr_noise.json | Lỗi/phát hiện: P20-1 hạng TN mốc nguyên; P20-2 ngoài phạm vi → tot_nghiep; P20-3 đăng ký niên luận; P20-4 OCR M2 từ chối thừa; Q-Real 0/400 chưa đạt | Sửa: P20-1 (v1.10, QD-14), P20-2, P20-3 — rformal C42–C46, integration E10–E16 | Q-Noise: P20-5 parser không dấu (chưa sửa)</t>
         </is>
       </c>
     </row>

--- a/Ke_hoach_nghien_cuu_CPA2_24_tuan.xlsx
+++ b/Ke_hoach_nghien_cuu_CPA2_24_tuan.xlsx
@@ -1963,7 +1963,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026: w20_benchmark/ — G-Truth v1 115 ca (114 chấm) + OCR-Noise v1 40 ca, gold viết tay + nguồn + oracle độc lập (41 tiền đề), loai_gold quy_che/thiet_ke, soát độc lập (không chạy hệ thống) rồi ĐÓNG BĂNG 312b7ff trước lần chạy đầu; không trùng w17; dev/test. Đầu vào baseline trung lập (baseline_dev/test.jsonl). Q-Real: pipeline nhập/ẩn danh xong, CHƯA ĐẠT 0/400 (chờ câu hỏi thật). Chạy dev: G-Truth Soundness 89,7% (6 unsound: P20-1 hạng tốt nghiệp mốc nguyên, P20-2/3 parser), OCR-Noise 100% sound, coverage 25% (M2 từ chối thừa). validate_benchmark ĐẠT. SỬA P20-1 (R-Formal v1.10: hạng so hữu tỉ theo cận dưới, QD-14 không làm tròn ĐTBCTL), P20-2 (parser không mặc định tot_nghiep → UNKNOWN 'chưa hỗ trợ'), P20-3 (đăng ký có tên HP chen giữa) — ca hồi quy fail với luật cũ; G-Truth dev sau sửa 100% sound (dev đã nhìn thấy; số chính thức = test, Tuần 22). Còn: Q-Real 0/400, P20-4. Mọi tuần 5–20 ĐẠT. | Q-Noise v1 (TỔNG HỢP, không thay Q-Real): 240 câu = 48 câu G-Truth × 5 kiểu gõ (gốc/bỏ dấu/viết tắt/gõ vội/bỏ dấu+viết tắt), gold kế thừa + ý định gán tay, đóng băng 5d8601c; dev: Sound 96,9%, Coverage 38,5% (V2/V4 0%), phát hiện P20-5 (4 unsound: luan van không dấu → tot_nghiep), chưa sửa.</t>
+          <t>18/10/2026: w20_benchmark/ — G-Truth v1 115 ca (114 chấm) + OCR-Noise v1 40 ca, gold viết tay + nguồn + oracle độc lập (41 tiền đề), loai_gold quy_che/thiet_ke, soát độc lập (không chạy hệ thống) rồi ĐÓNG BĂNG 312b7ff trước lần chạy đầu; không trùng w17; dev/test. Đầu vào baseline trung lập (baseline_dev/test.jsonl). Q-Real: pipeline nhập/ẩn danh xong, CHƯA ĐẠT 0/400 (chờ câu hỏi thật). Chạy dev: G-Truth Soundness 89,7% (6 unsound: P20-1 hạng tốt nghiệp mốc nguyên, P20-2/3 parser), OCR-Noise 100% sound, coverage 25% (M2 từ chối thừa). validate_benchmark ĐẠT. SỬA P20-1 (R-Formal v1.10: hạng so hữu tỉ theo cận dưới, QD-14 không làm tròn ĐTBCTL), P20-2 (parser không mặc định tot_nghiep → UNKNOWN 'chưa hỗ trợ'), P20-3 (đăng ký có tên HP chen giữa) — ca hồi quy fail với luật cũ; G-Truth dev sau sửa 100% sound (dev đã nhìn thấy; số chính thức = test, Tuần 22). Còn: Q-Real 0/400, P20-4. Mọi tuần 5–20 ĐẠT. | Q-Noise v1 (TỔNG HỢP, không thay Q-Real): 240 câu = 48 câu G-Truth × 5 kiểu gõ (gốc/bỏ dấu/viết tắt/gõ vội/bỏ dấu+viết tắt), gold kế thừa + ý định gán tay, đóng băng 5d8601c; dev: Sound 96,9%, Coverage 38,5% (V2/V4 0%), phát hiện P20-5 (4 unsound: luan van không dấu → tot_nghiep) → đã sửa (parser chuẩn hoá bỏ dấu từ khoá + viết tắt theo ngữ cảnh, E17–E28, 2 lượt review); sau sửa (dev đã thấy, file _sau_P20-5): Q-Noise 100% sound / 88,5% coverage, G-Truth không đổi.</t>
         </is>
       </c>
     </row>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Đọc: không | Code: build_benchmark.py, validate_benchmark.py, run_cpa2.py, baseline.py, nhap_qreal.py | Test: validate_benchmark B1–B10 ĐẠT | Artifact: Tuan20_Benchmark.md, gtruth.json, ocr_noise.json | Lỗi/phát hiện: P20-1 hạng TN mốc nguyên; P20-2 ngoài phạm vi → tot_nghiep; P20-3 đăng ký niên luận; P20-4 OCR M2 từ chối thừa; Q-Real 0/400 chưa đạt | Sửa: P20-1 (v1.10, QD-14), P20-2, P20-3 — rformal C42–C46, integration E10–E16 | Q-Noise: P20-5 parser không dấu (chưa sửa)</t>
+          <t>Đọc: không | Code: build_benchmark.py, validate_benchmark.py, run_cpa2.py, baseline.py, nhap_qreal.py | Test: validate_benchmark B1–B10 ĐẠT | Artifact: Tuan20_Benchmark.md, gtruth.json, ocr_noise.json | Lỗi/phát hiện: P20-1 hạng TN mốc nguyên; P20-2 ngoài phạm vi → tot_nghiep; P20-3 đăng ký niên luận; P20-4 OCR M2 từ chối thừa; Q-Real 0/400 chưa đạt | Sửa: P20-1 (v1.10, QD-14), P20-2, P20-3 — rformal C42–C46, integration E10–E16 | Q-Noise: P20-5 parser không dấu → đã sửa, integration E17–E28</t>
         </is>
       </c>
     </row>

--- a/Ke_hoach_nghien_cuu_CPA2_24_tuan.xlsx
+++ b/Ke_hoach_nghien_cuu_CPA2_24_tuan.xlsx
@@ -1963,7 +1963,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026: w20_benchmark/ — G-Truth v1 115 ca (114 chấm) + OCR-Noise v1 40 ca, gold viết tay + nguồn + oracle độc lập (41 tiền đề), loai_gold quy_che/thiet_ke, soát độc lập (không chạy hệ thống) rồi ĐÓNG BĂNG 312b7ff trước lần chạy đầu; không trùng w17; dev/test. Đầu vào baseline trung lập (baseline_dev/test.jsonl). Q-Real: pipeline nhập/ẩn danh xong, CHƯA ĐẠT 0/400 (chờ câu hỏi thật). Chạy dev: G-Truth Soundness 89,7% (6 unsound: P20-1 hạng tốt nghiệp mốc nguyên, P20-2/3 parser), OCR-Noise 100% sound, coverage 25% (M2 từ chối thừa). validate_benchmark ĐẠT. SỬA P20-1 (R-Formal v1.10: hạng so hữu tỉ theo cận dưới, QD-14 không làm tròn ĐTBCTL), P20-2 (parser không mặc định tot_nghiep → UNKNOWN 'chưa hỗ trợ'), P20-3 (đăng ký có tên HP chen giữa) — ca hồi quy fail với luật cũ; G-Truth dev sau sửa 100% sound (dev đã nhìn thấy; số chính thức = test, Tuần 22). Còn: Q-Real 0/400, P20-4. Mọi tuần 5–20 ĐẠT. | Q-Noise v1 (TỔNG HỢP, không thay Q-Real): 240 câu = 48 câu G-Truth × 5 kiểu gõ (gốc/bỏ dấu/viết tắt/gõ vội/bỏ dấu+viết tắt), gold kế thừa + ý định gán tay, đóng băng 5d8601c; dev: Sound 96,9%, Coverage 38,5% (V2/V4 0%), phát hiện P20-5 (4 unsound: luan van không dấu → tot_nghiep) → đã sửa (parser chuẩn hoá bỏ dấu từ khoá + viết tắt theo ngữ cảnh, E17–E28, 2 lượt review); sau sửa (dev đã thấy, file _sau_P20-5): Q-Noise 100% sound / 88,5% coverage, G-Truth không đổi.</t>
+          <t>18/10/2026: w20_benchmark/ — G-Truth v1 115 ca (114 chấm) + OCR-Noise v1 40 ca, gold viết tay + nguồn + oracle độc lập (41 tiền đề), loai_gold quy_che/thiet_ke, soát độc lập (không chạy hệ thống) rồi ĐÓNG BĂNG 312b7ff trước lần chạy đầu; không trùng w17; dev/test. Đầu vào baseline trung lập (baseline_dev/test.jsonl). Q-Real: pipeline nhập/ẩn danh xong, CHƯA ĐẠT 0/400 (chờ câu hỏi thật). Chạy dev: G-Truth Soundness 89,7% (6 unsound: P20-1 hạng tốt nghiệp mốc nguyên, P20-2/3 parser), OCR-Noise 100% sound, coverage 25% (M2 từ chối thừa). validate_benchmark ĐẠT. SỬA P20-1 (R-Formal v1.10: hạng so hữu tỉ theo cận dưới, QD-14 không làm tròn ĐTBCTL), P20-2 (parser không mặc định tot_nghiep → UNKNOWN 'chưa hỗ trợ'), P20-3 (đăng ký có tên HP chen giữa) — ca hồi quy fail với luật cũ; G-Truth dev sau sửa 100% sound (dev đã nhìn thấy; số chính thức = test, Tuần 22). Còn: Q-Real 0/400, P20-4. Mọi tuần 5–20 ĐẠT. | Q-Noise v1 (TỔNG HỢP, không thay Q-Real): 240 câu = 48 câu G-Truth × 5 kiểu gõ (gốc/bỏ dấu/viết tắt/gõ vội/bỏ dấu+viết tắt), gold kế thừa + ý định gán tay, đóng băng 5d8601c; dev: Sound 96,9%, Coverage 38,5% (V2/V4 0%), phát hiện P20-5 (4 unsound: luan van không dấu → tot_nghiep) → đã sửa (parser chuẩn hoá bỏ dấu từ khoá + viết tắt theo ngữ cảnh, E17–E28, 2 lượt review); sau sửa (dev đã thấy, file _sau_P20-5): Q-Noise 100% sound / 88,5% coverage, G-Truth không đổi. | 19/10/2026: Google Form thu câu hỏi (đồng ý NĐ 13/2023, mã rút lại, câu tự do trước kịch bản) + Q-Elicit 20 kịch bản đóng băng (báo riêng, không tính); Q-Real vẫn chưa đạt 0/400 — chờ Loi phát form.</t>
         </is>
       </c>
     </row>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Đọc: không | Code: build_benchmark.py, validate_benchmark.py, run_cpa2.py, baseline.py, nhap_qreal.py | Test: validate_benchmark B1–B10 ĐẠT | Artifact: Tuan20_Benchmark.md, gtruth.json, ocr_noise.json | Lỗi/phát hiện: P20-1 hạng TN mốc nguyên; P20-2 ngoài phạm vi → tot_nghiep; P20-3 đăng ký niên luận; P20-4 OCR M2 từ chối thừa; Q-Real 0/400 chưa đạt | Sửa: P20-1 (v1.10, QD-14), P20-2, P20-3 — rformal C42–C46, integration E10–E16 | Q-Noise: P20-5 parser không dấu → đã sửa, integration E17–E28</t>
+          <t>Đọc: không | Code: build_benchmark.py, validate_benchmark.py, run_cpa2.py, baseline.py, nhap_qreal.py | Test: validate_benchmark B1–B11 ĐẠT | Artifact: Tuan20_Benchmark.md, gtruth.json, ocr_noise.json | Lỗi/phát hiện: P20-1 hạng TN mốc nguyên; P20-2 ngoài phạm vi → tot_nghiep; P20-3 đăng ký niên luận; P20-4 OCR M2 từ chối thừa; Q-Real 0/400 chưa đạt | Sửa: P20-1 (v1.10, QD-14), P20-2, P20-3 — rformal C42–C46, integration E10–E16 | Q-Noise: P20-5 parser không dấu → đã sửa, integration E17–E28</t>
         </is>
       </c>
     </row>

--- a/Ke_hoach_nghien_cuu_CPA2_24_tuan.xlsx
+++ b/Ke_hoach_nghien_cuu_CPA2_24_tuan.xlsx
@@ -1963,7 +1963,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026: w20_benchmark/ — G-Truth v1 115 ca (114 chấm) + OCR-Noise v1 40 ca, gold viết tay + nguồn + oracle độc lập (41 tiền đề), loai_gold quy_che/thiet_ke, soát độc lập (không chạy hệ thống) rồi ĐÓNG BĂNG 312b7ff trước lần chạy đầu; không trùng w17; dev/test. Đầu vào baseline trung lập (baseline_dev/test.jsonl). Q-Real: pipeline nhập/ẩn danh xong, CHƯA ĐẠT 0/400 (chờ câu hỏi thật). Chạy dev: G-Truth Soundness 89,7% (6 unsound: P20-1 hạng tốt nghiệp mốc nguyên, P20-2/3 parser), OCR-Noise 100% sound, coverage 25% (M2 từ chối thừa). validate_benchmark ĐẠT. SỬA P20-1 (R-Formal v1.10: hạng so hữu tỉ theo cận dưới, QD-14 không làm tròn ĐTBCTL), P20-2 (parser không mặc định tot_nghiep → UNKNOWN 'chưa hỗ trợ'), P20-3 (đăng ký có tên HP chen giữa) — ca hồi quy fail với luật cũ; G-Truth dev sau sửa 100% sound (dev đã nhìn thấy; số chính thức = test, Tuần 22). Còn: Q-Real 0/400, P20-4. Mọi tuần 5–20 ĐẠT. | Q-Noise v1 (TỔNG HỢP, không thay Q-Real): 240 câu = 48 câu G-Truth × 5 kiểu gõ (gốc/bỏ dấu/viết tắt/gõ vội/bỏ dấu+viết tắt), gold kế thừa + ý định gán tay, đóng băng 5d8601c; dev: Sound 96,9%, Coverage 38,5% (V2/V4 0%), phát hiện P20-5 (4 unsound: luan van không dấu → tot_nghiep) → đã sửa (parser chuẩn hoá bỏ dấu từ khoá + viết tắt theo ngữ cảnh, E17–E28, 2 lượt review); sau sửa (dev đã thấy, file _sau_P20-5): Q-Noise 100% sound / 88,5% coverage, G-Truth không đổi. | 19/10/2026: Google Form thu câu hỏi (đồng ý NĐ 13/2023, mã rút lại, câu tự do trước kịch bản) + Q-Elicit 20 kịch bản đóng băng (báo riêng, không tính); Q-Real vẫn chưa đạt 0/400 — chờ Loi phát form.</t>
+          <t>18/10/2026: w20_benchmark/ — G-Truth v1 115 ca (114 chấm) + OCR-Noise v1 40 ca, gold viết tay + nguồn + oracle độc lập (41 tiền đề), loai_gold quy_che/thiet_ke, soát độc lập (không chạy hệ thống) rồi ĐÓNG BĂNG 312b7ff trước lần chạy đầu; không trùng w17; dev/test. Đầu vào baseline trung lập (baseline_dev/test.jsonl). Q-Real: pipeline nhập/ẩn danh xong, CHƯA ĐẠT 0/400 (chờ câu hỏi thật). Chạy dev: G-Truth Soundness 89,7% (6 unsound: P20-1 hạng tốt nghiệp mốc nguyên, P20-2/3 parser), OCR-Noise 100% sound, coverage 25% (M2 từ chối thừa). validate_benchmark ĐẠT. SỬA P20-1 (R-Formal v1.10: hạng so hữu tỉ theo cận dưới, QD-14 không làm tròn ĐTBCTL), P20-2 (parser không mặc định tot_nghiep → UNKNOWN 'chưa hỗ trợ'), P20-3 (đăng ký có tên HP chen giữa) — ca hồi quy fail với luật cũ; G-Truth dev sau sửa 100% sound (dev đã nhìn thấy; số chính thức = test, Tuần 22). Còn: Q-Real 0/400, P20-4. Mọi tuần 5–20 ĐẠT. | Q-Noise v1 (TỔNG HỢP, không thay Q-Real): 240 câu = 48 câu G-Truth × 5 kiểu gõ (gốc/bỏ dấu/viết tắt/gõ vội/bỏ dấu+viết tắt), gold kế thừa + ý định gán tay, đóng băng 5d8601c; dev: Sound 96,9%, Coverage 38,5% (V2/V4 0%), phát hiện P20-5 (4 unsound: luan van không dấu → tot_nghiep) → đã sửa (parser chuẩn hoá bỏ dấu từ khoá + viết tắt theo ngữ cảnh, E17–E28, 2 lượt review); sau sửa (dev đã thấy, file _sau_P20-5): Q-Noise 100% sound / 88,5% coverage, G-Truth không đổi. | 19/10/2026: Google Form thu câu hỏi (đồng ý NĐ 13/2023, mã rút lại, câu tự do trước kịch bản) + Q-Elicit 20 kịch bản đóng băng (báo riêng, không tính); Q-Real vẫn chưa đạt 0/400 — chờ Loi phát form. | P20-4 (A): mất ĐTBCHK vẫn không tin điểm (M2 ≡ F1), hỏi 1 số ĐTBCHK in thay 5–7 HP, nhận khai báo số in (validate_ocr F5–F11); OCR-Noise dev không đổi (M2 0% coverage), mô phỏng trả lời → 5/5 TRUE. Phương án B (số tích lũy) lập kế hoạch riêng.</t>
         </is>
       </c>
     </row>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Đọc: không | Code: build_benchmark.py, validate_benchmark.py, run_cpa2.py, baseline.py, nhap_qreal.py | Test: validate_benchmark B1–B11 ĐẠT | Artifact: Tuan20_Benchmark.md, gtruth.json, ocr_noise.json | Lỗi/phát hiện: P20-1 hạng TN mốc nguyên; P20-2 ngoài phạm vi → tot_nghiep; P20-3 đăng ký niên luận; P20-4 OCR M2 từ chối thừa; Q-Real 0/400 chưa đạt | Sửa: P20-1 (v1.10, QD-14), P20-2, P20-3 — rformal C42–C46, integration E10–E16 | Q-Noise: P20-5 parser không dấu → đã sửa, integration E17–E28</t>
+          <t>Đọc: không | Code: build_benchmark.py, validate_benchmark.py, run_cpa2.py, baseline.py, nhap_qreal.py | Test: validate_benchmark B1–B11 ĐẠT | Artifact: Tuan20_Benchmark.md, gtruth.json, ocr_noise.json | Lỗi/phát hiện: P20-1 hạng TN mốc nguyên; P20-2 ngoài phạm vi → tot_nghiep; P20-3 đăng ký niên luận; P20-4 OCR M2 từ chối thừa; Q-Real 0/400 chưa đạt | Sửa: P20-1 (v1.10, QD-14), P20-2, P20-3 — rformal C42–C46, integration E10–E16 | Q-Noise: P20-5 parser không dấu → đã sửa, integration E17–E28 | P20-4: w15 F5–F11</t>
         </is>
       </c>
     </row>

--- a/Ke_hoach_nghien_cuu_CPA2_24_tuan.xlsx
+++ b/Ke_hoach_nghien_cuu_CPA2_24_tuan.xlsx
@@ -1963,7 +1963,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026: w20_benchmark/ — G-Truth v1 115 ca (114 chấm) + OCR-Noise v1 40 ca, gold viết tay + nguồn + oracle độc lập (41 tiền đề), loai_gold quy_che/thiet_ke, soát độc lập (không chạy hệ thống) rồi ĐÓNG BĂNG 312b7ff trước lần chạy đầu; không trùng w17; dev/test. Đầu vào baseline trung lập (baseline_dev/test.jsonl). Q-Real: pipeline nhập/ẩn danh xong, CHƯA ĐẠT 0/400 (chờ câu hỏi thật). Chạy dev: G-Truth Soundness 89,7% (6 unsound: P20-1 hạng tốt nghiệp mốc nguyên, P20-2/3 parser), OCR-Noise 100% sound, coverage 25% (M2 từ chối thừa). validate_benchmark ĐẠT. SỬA P20-1 (R-Formal v1.10: hạng so hữu tỉ theo cận dưới, QD-14 không làm tròn ĐTBCTL), P20-2 (parser không mặc định tot_nghiep → UNKNOWN 'chưa hỗ trợ'), P20-3 (đăng ký có tên HP chen giữa) — ca hồi quy fail với luật cũ; G-Truth dev sau sửa 100% sound (dev đã nhìn thấy; số chính thức = test, Tuần 22). Còn: Q-Real 0/400, P20-4. Mọi tuần 5–20 ĐẠT. | Q-Noise v1 (TỔNG HỢP, không thay Q-Real): 240 câu = 48 câu G-Truth × 5 kiểu gõ (gốc/bỏ dấu/viết tắt/gõ vội/bỏ dấu+viết tắt), gold kế thừa + ý định gán tay, đóng băng 5d8601c; dev: Sound 96,9%, Coverage 38,5% (V2/V4 0%), phát hiện P20-5 (4 unsound: luan van không dấu → tot_nghiep) → đã sửa (parser chuẩn hoá bỏ dấu từ khoá + viết tắt theo ngữ cảnh, E17–E28, 2 lượt review); sau sửa (dev đã thấy, file _sau_P20-5): Q-Noise 100% sound / 88,5% coverage, G-Truth không đổi. | 19/10/2026: Google Form thu câu hỏi (đồng ý NĐ 13/2023, mã rút lại, câu tự do trước kịch bản) + Q-Elicit 20 kịch bản đóng băng (báo riêng, không tính); Q-Real vẫn chưa đạt 0/400 — chờ Loi phát form. | P20-4 (A): mất ĐTBCHK vẫn không tin điểm (M2 ≡ F1), hỏi 1 số ĐTBCHK in thay 5–7 HP, nhận khai báo số in (validate_ocr F5–F11); OCR-Noise dev không đổi (M2 0% coverage), mô phỏng trả lời → 5/5 TRUE. Phương án B (số tích lũy) lập kế hoạch riêng.</t>
+          <t>18/10/2026: w20_benchmark/ — G-Truth v1 115 ca (114 chấm) + OCR-Noise v1 40 ca, gold viết tay + nguồn + oracle độc lập (41 tiền đề), loai_gold quy_che/thiet_ke, soát độc lập (không chạy hệ thống) rồi ĐÓNG BĂNG 312b7ff trước lần chạy đầu; không trùng w17; dev/test. Đầu vào baseline trung lập (baseline_dev/test.jsonl). Q-Real: pipeline nhập/ẩn danh xong, CHƯA ĐẠT 0/400 (chờ câu hỏi thật). Chạy dev: G-Truth Soundness 89,7% (6 unsound: P20-1 hạng tốt nghiệp mốc nguyên, P20-2/3 parser), OCR-Noise 100% sound, coverage 25% (M2 từ chối thừa). validate_benchmark ĐẠT. SỬA P20-1 (R-Formal v1.10: hạng so hữu tỉ theo cận dưới, QD-14 không làm tròn ĐTBCTL), P20-2 (parser không mặc định tot_nghiep → UNKNOWN 'chưa hỗ trợ'), P20-3 (đăng ký có tên HP chen giữa) — ca hồi quy fail với luật cũ; G-Truth dev sau sửa 100% sound (dev đã nhìn thấy; số chính thức = test, Tuần 22). Còn: Q-Real 0/400, P20-4. Mọi tuần 5–20 ĐẠT. | Q-Noise v1 (TỔNG HỢP, không thay Q-Real): 240 câu = 48 câu G-Truth × 5 kiểu gõ (gốc/bỏ dấu/viết tắt/gõ vội/bỏ dấu+viết tắt), gold kế thừa + ý định gán tay, đóng băng 5d8601c; dev: Sound 96,9%, Coverage 38,5% (V2/V4 0%), phát hiện P20-5 (4 unsound: luan van không dấu → tot_nghiep) → đã sửa (parser chuẩn hoá bỏ dấu từ khoá + viết tắt theo ngữ cảnh, E17–E28, 2 lượt review); sau sửa (dev đã thấy, file _sau_P20-5): Q-Noise 100% sound / 88,5% coverage, G-Truth không đổi. | 19/10/2026: Google Form thu câu hỏi (đồng ý NĐ 13/2023, mã rút lại, câu tự do trước kịch bản) + Q-Elicit 20 kịch bản đóng băng (báo riêng, không tính); Q-Real vẫn chưa đạt 0/400 — chờ Loi phát form. | P20-4 (A): mất ĐTBCHK vẫn không tin điểm (M2 ≡ F1), hỏi 1 số ĐTBCHK in thay 5–7 HP, nhận khai báo số in (validate_ocr F5–F11); OCR-Noise dev không đổi (M2 0% coverage), mô phỏng trả lời → 5/5 TRUE. Phương án B (số tích lũy) lập kế hoạch riêng. | C12: ý định xếp loại tốt nghiệp (QD-15 đúng hạng; E29–E37); review phát hiện C15 — KB không hạ bậc (tc_diem_f không sinh, Đ34 k2 b chưa hình thức hoá) → prototype trả UNKNOWN với hạng gốc XS/G; sửa R-Formal lập kế hoạch riêng (ảnh hưởng gold HG).</t>
         </is>
       </c>
     </row>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Đọc: không | Code: build_benchmark.py, validate_benchmark.py, run_cpa2.py, baseline.py, nhap_qreal.py | Test: validate_benchmark B1–B11 ĐẠT | Artifact: Tuan20_Benchmark.md, gtruth.json, ocr_noise.json | Lỗi/phát hiện: P20-1 hạng TN mốc nguyên; P20-2 ngoài phạm vi → tot_nghiep; P20-3 đăng ký niên luận; P20-4 OCR M2 từ chối thừa; Q-Real 0/400 chưa đạt | Sửa: P20-1 (v1.10, QD-14), P20-2, P20-3 — rformal C42–C46, integration E10–E16 | Q-Noise: P20-5 parser không dấu → đã sửa, integration E17–E28 | P20-4: w15 F5–F11</t>
+          <t>Đọc: không | Code: build_benchmark.py, validate_benchmark.py, run_cpa2.py, baseline.py, nhap_qreal.py | Test: validate_benchmark B1–B11 ĐẠT | Artifact: Tuan20_Benchmark.md, gtruth.json, ocr_noise.json | Lỗi/phát hiện: P20-1 hạng TN mốc nguyên; P20-2 ngoài phạm vi → tot_nghiep; P20-3 đăng ký niên luận; P20-4 OCR M2 từ chối thừa; Q-Real 0/400 chưa đạt | Sửa: P20-1 (v1.10, QD-14), P20-2, P20-3 — rformal C42–C46, integration E10–E16 | Q-Noise: P20-5 parser không dấu → đã sửa, integration E17–E28 | P20-4: w15 F5–F11 | C12: integration E29–E37, QD-15</t>
         </is>
       </c>
     </row>

--- a/Ke_hoach_nghien_cuu_CPA2_24_tuan.xlsx
+++ b/Ke_hoach_nghien_cuu_CPA2_24_tuan.xlsx
@@ -1963,7 +1963,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026: w20_benchmark/ — G-Truth v1 115 ca (114 chấm) + OCR-Noise v1 40 ca, gold viết tay + nguồn + oracle độc lập (41 tiền đề), loai_gold quy_che/thiet_ke, soát độc lập (không chạy hệ thống) rồi ĐÓNG BĂNG 312b7ff trước lần chạy đầu; không trùng w17; dev/test. Đầu vào baseline trung lập (baseline_dev/test.jsonl). Q-Real: pipeline nhập/ẩn danh xong, CHƯA ĐẠT 0/400 (chờ câu hỏi thật). Chạy dev: G-Truth Soundness 89,7% (6 unsound: P20-1 hạng tốt nghiệp mốc nguyên, P20-2/3 parser), OCR-Noise 100% sound, coverage 25% (M2 từ chối thừa). validate_benchmark ĐẠT. SỬA P20-1 (R-Formal v1.10: hạng so hữu tỉ theo cận dưới, QD-14 không làm tròn ĐTBCTL), P20-2 (parser không mặc định tot_nghiep → UNKNOWN 'chưa hỗ trợ'), P20-3 (đăng ký có tên HP chen giữa) — ca hồi quy fail với luật cũ; G-Truth dev sau sửa 100% sound (dev đã nhìn thấy; số chính thức = test, Tuần 22). Còn: Q-Real 0/400, P20-4. Mọi tuần 5–20 ĐẠT. | Q-Noise v1 (TỔNG HỢP, không thay Q-Real): 240 câu = 48 câu G-Truth × 5 kiểu gõ (gốc/bỏ dấu/viết tắt/gõ vội/bỏ dấu+viết tắt), gold kế thừa + ý định gán tay, đóng băng 5d8601c; dev: Sound 96,9%, Coverage 38,5% (V2/V4 0%), phát hiện P20-5 (4 unsound: luan van không dấu → tot_nghiep) → đã sửa (parser chuẩn hoá bỏ dấu từ khoá + viết tắt theo ngữ cảnh, E17–E28, 2 lượt review); sau sửa (dev đã thấy, file _sau_P20-5): Q-Noise 100% sound / 88,5% coverage, G-Truth không đổi. | 19/10/2026: Google Form thu câu hỏi (đồng ý NĐ 13/2023, mã rút lại, câu tự do trước kịch bản) + Q-Elicit 20 kịch bản đóng băng (báo riêng, không tính); Q-Real vẫn chưa đạt 0/400 — chờ Loi phát form. | P20-4 (A): mất ĐTBCHK vẫn không tin điểm (M2 ≡ F1), hỏi 1 số ĐTBCHK in thay 5–7 HP, nhận khai báo số in (validate_ocr F5–F11); OCR-Noise dev không đổi (M2 0% coverage), mô phỏng trả lời → 5/5 TRUE. Phương án B (số tích lũy) lập kế hoạch riêng. | C12: ý định xếp loại tốt nghiệp (QD-15 đúng hạng; E29–E37); review phát hiện C15 — KB không hạ bậc (tc_diem_f không sinh, Đ34 k2 b chưa hình thức hoá) → prototype trả UNKNOWN với hạng gốc XS/G; sửa R-Formal lập kế hoạch riêng (ảnh hưởng gold HG).</t>
+          <t>18/10/2026: w20_benchmark/ — G-Truth v1 115 ca (114 chấm) + OCR-Noise v1 40 ca, gold viết tay + nguồn + oracle độc lập (41 tiền đề), loai_gold quy_che/thiet_ke, soát độc lập (không chạy hệ thống) rồi ĐÓNG BĂNG 312b7ff trước lần chạy đầu; không trùng w17; dev/test. Đầu vào baseline trung lập (baseline_dev/test.jsonl). Q-Real: pipeline nhập/ẩn danh xong, CHƯA ĐẠT 0/400 (chờ câu hỏi thật). Chạy dev: G-Truth Soundness 89,7% (6 unsound: P20-1 hạng tốt nghiệp mốc nguyên, P20-2/3 parser), OCR-Noise 100% sound, coverage 25% (M2 từ chối thừa). validate_benchmark ĐẠT. SỬA P20-1 (R-Formal v1.10: hạng so hữu tỉ theo cận dưới, QD-14 không làm tròn ĐTBCTL), P20-2 (parser không mặc định tot_nghiep → UNKNOWN 'chưa hỗ trợ'), P20-3 (đăng ký có tên HP chen giữa) — ca hồi quy fail với luật cũ; G-Truth dev sau sửa 100% sound (dev đã nhìn thấy; số chính thức = test, Tuần 22). Còn: Q-Real 0/400, P20-4. Mọi tuần 5–20 ĐẠT. | Q-Noise v1 (TỔNG HỢP, không thay Q-Real): 240 câu = 48 câu G-Truth × 5 kiểu gõ (gốc/bỏ dấu/viết tắt/gõ vội/bỏ dấu+viết tắt), gold kế thừa + ý định gán tay, đóng băng 5d8601c; dev: Sound 96,9%, Coverage 38,5% (V2/V4 0%), phát hiện P20-5 (4 unsound: luan van không dấu → tot_nghiep) → đã sửa (parser chuẩn hoá bỏ dấu từ khoá + viết tắt theo ngữ cảnh, E17–E28, 2 lượt review); sau sửa (dev đã thấy, file _sau_P20-5): Q-Noise 100% sound / 88,5% coverage, G-Truth không đổi. | 19/10/2026: Google Form thu câu hỏi (đồng ý NĐ 13/2023, mã rút lại, câu tự do trước kịch bản) + Q-Elicit 20 kịch bản đóng băng (báo riêng, không tính); Q-Real vẫn chưa đạt 0/400 — chờ Loi phát form. | P20-4 (A): mất ĐTBCHK vẫn không tin điểm (M2 ≡ F1), hỏi 1 số ĐTBCHK in thay 5–7 HP, nhận khai báo số in (validate_ocr F5–F11); OCR-Noise dev không đổi (M2 0% coverage), mô phỏng trả lời → 5/5 TRUE. Phương án B (số tích lũy) lập kế hoạch riêng. | C12: ý định xếp loại tốt nghiệp (QD-15 đúng hạng; E29–E37); review phát hiện C15 — KB không hạ bậc (tc_diem_f không sinh, Đ34 k2 b chưa hình thức hoá) → prototype trả UNKNOWN với hạng gốc XS/G; sửa R-Formal lập kế hoạch riêng (ảnh hưởng gold HG). | C15: R-Formal v1.11 — hạ bậc Đ34 k2 a+b (HP điểm cuối F chắc chắn; tc_diem_f, kỷ luật cấp Trường là khai báo; chưa khai báo → mở nhánh), R-F07b; errata G-Truth HG-02/03/04/08; dev chính thức 57/58 (HG-03 từ chối thừa), theo errata 58/58. A17 hỏi HP điều kiện.</t>
         </is>
       </c>
     </row>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Đọc: không | Code: build_benchmark.py, validate_benchmark.py, run_cpa2.py, baseline.py, nhap_qreal.py | Test: validate_benchmark B1–B11 ĐẠT | Artifact: Tuan20_Benchmark.md, gtruth.json, ocr_noise.json | Lỗi/phát hiện: P20-1 hạng TN mốc nguyên; P20-2 ngoài phạm vi → tot_nghiep; P20-3 đăng ký niên luận; P20-4 OCR M2 từ chối thừa; Q-Real 0/400 chưa đạt | Sửa: P20-1 (v1.10, QD-14), P20-2, P20-3 — rformal C42–C46, integration E10–E16 | Q-Noise: P20-5 parser không dấu → đã sửa, integration E17–E28 | P20-4: w15 F5–F11 | C12: integration E29–E37, QD-15</t>
+          <t>Đọc: không | Code: build_benchmark.py, validate_benchmark.py, run_cpa2.py, baseline.py, nhap_qreal.py | Test: validate_benchmark B1–B11 ĐẠT | Artifact: Tuan20_Benchmark.md, gtruth.json, ocr_noise.json | Lỗi/phát hiện: P20-1 hạng TN mốc nguyên; P20-2 ngoài phạm vi → tot_nghiep; P20-3 đăng ký niên luận; P20-4 OCR M2 từ chối thừa; Q-Real 0/400 chưa đạt | Sửa: P20-1 (v1.10, QD-14), P20-2, P20-3 — rformal C42–C46, integration E10–E16 | Q-Noise: P20-5 parser không dấu → đã sửa, integration E17–E28 | P20-4: w15 F5–F11 | C12: integration E29–E37, QD-15 | C15: rformal C47–C53, graduation D1–D4, student_facts L5, integration E42</t>
         </is>
       </c>
     </row>

--- a/Ke_hoach_nghien_cuu_CPA2_24_tuan.xlsx
+++ b/Ke_hoach_nghien_cuu_CPA2_24_tuan.xlsx
@@ -1963,7 +1963,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18/10/2026: w20_benchmark/ — G-Truth v1 115 ca (114 chấm) + OCR-Noise v1 40 ca, gold viết tay + nguồn + oracle độc lập (41 tiền đề), loai_gold quy_che/thiet_ke, soát độc lập (không chạy hệ thống) rồi ĐÓNG BĂNG 312b7ff trước lần chạy đầu; không trùng w17; dev/test. Đầu vào baseline trung lập (baseline_dev/test.jsonl). Q-Real: pipeline nhập/ẩn danh xong, CHƯA ĐẠT 0/400 (chờ câu hỏi thật). Chạy dev: G-Truth Soundness 89,7% (6 unsound: P20-1 hạng tốt nghiệp mốc nguyên, P20-2/3 parser), OCR-Noise 100% sound, coverage 25% (M2 từ chối thừa). validate_benchmark ĐẠT. SỬA P20-1 (R-Formal v1.10: hạng so hữu tỉ theo cận dưới, QD-14 không làm tròn ĐTBCTL), P20-2 (parser không mặc định tot_nghiep → UNKNOWN 'chưa hỗ trợ'), P20-3 (đăng ký có tên HP chen giữa) — ca hồi quy fail với luật cũ; G-Truth dev sau sửa 100% sound (dev đã nhìn thấy; số chính thức = test, Tuần 22). Còn: Q-Real 0/400, P20-4. Mọi tuần 5–20 ĐẠT. | Q-Noise v1 (TỔNG HỢP, không thay Q-Real): 240 câu = 48 câu G-Truth × 5 kiểu gõ (gốc/bỏ dấu/viết tắt/gõ vội/bỏ dấu+viết tắt), gold kế thừa + ý định gán tay, đóng băng 5d8601c; dev: Sound 96,9%, Coverage 38,5% (V2/V4 0%), phát hiện P20-5 (4 unsound: luan van không dấu → tot_nghiep) → đã sửa (parser chuẩn hoá bỏ dấu từ khoá + viết tắt theo ngữ cảnh, E17–E28, 2 lượt review); sau sửa (dev đã thấy, file _sau_P20-5): Q-Noise 100% sound / 88,5% coverage, G-Truth không đổi. | 19/10/2026: Google Form thu câu hỏi (đồng ý NĐ 13/2023, mã rút lại, câu tự do trước kịch bản) + Q-Elicit 20 kịch bản đóng băng (báo riêng, không tính); Q-Real vẫn chưa đạt 0/400 — chờ Loi phát form. | P20-4 (A): mất ĐTBCHK vẫn không tin điểm (M2 ≡ F1), hỏi 1 số ĐTBCHK in thay 5–7 HP, nhận khai báo số in (validate_ocr F5–F11); OCR-Noise dev không đổi (M2 0% coverage), mô phỏng trả lời → 5/5 TRUE. Phương án B (số tích lũy) lập kế hoạch riêng. | C12: ý định xếp loại tốt nghiệp (QD-15 đúng hạng; E29–E37); review phát hiện C15 — KB không hạ bậc (tc_diem_f không sinh, Đ34 k2 b chưa hình thức hoá) → prototype trả UNKNOWN với hạng gốc XS/G; sửa R-Formal lập kế hoạch riêng (ảnh hưởng gold HG). | C15: R-Formal v1.11 — hạ bậc Đ34 k2 a+b (HP điểm cuối F chắc chắn; tc_diem_f, kỷ luật cấp Trường là khai báo; chưa khai báo → mở nhánh), R-F07b; errata G-Truth HG-02/03/04/08; dev chính thức 57/58 (HG-03 từ chối thừa), theo errata 58/58. A17 hỏi HP điều kiện.</t>
+          <t>18/10/2026: w20_benchmark/ — G-Truth v1 115 ca (114 chấm) + OCR-Noise v1 40 ca, gold viết tay + nguồn + oracle độc lập (41 tiền đề), loai_gold quy_che/thiet_ke, soát độc lập (không chạy hệ thống) rồi ĐÓNG BĂNG 312b7ff trước lần chạy đầu; không trùng w17; dev/test. Đầu vào baseline trung lập (baseline_dev/test.jsonl). Q-Real: pipeline nhập/ẩn danh xong, CHƯA ĐẠT 0/400 (chờ câu hỏi thật). Chạy dev: G-Truth Soundness 89,7% (6 unsound: P20-1 hạng tốt nghiệp mốc nguyên, P20-2/3 parser), OCR-Noise 100% sound, coverage 25% (M2 từ chối thừa). validate_benchmark ĐẠT. SỬA P20-1 (R-Formal v1.10: hạng so hữu tỉ theo cận dưới, QD-14 không làm tròn ĐTBCTL), P20-2 (parser không mặc định tot_nghiep → UNKNOWN 'chưa hỗ trợ'), P20-3 (đăng ký có tên HP chen giữa) — ca hồi quy fail với luật cũ; G-Truth dev sau sửa 100% sound (dev đã nhìn thấy; số chính thức = test, Tuần 22). Còn: Q-Real 0/400, P20-4. Mọi tuần 5–20 ĐẠT. | Q-Noise v1 (TỔNG HỢP, không thay Q-Real): 240 câu = 48 câu G-Truth × 5 kiểu gõ (gốc/bỏ dấu/viết tắt/gõ vội/bỏ dấu+viết tắt), gold kế thừa + ý định gán tay, đóng băng 5d8601c; dev: Sound 96,9%, Coverage 38,5% (V2/V4 0%), phát hiện P20-5 (4 unsound: luan van không dấu → tot_nghiep) → đã sửa (parser chuẩn hoá bỏ dấu từ khoá + viết tắt theo ngữ cảnh, E17–E28, 2 lượt review); sau sửa (dev đã thấy, file _sau_P20-5): Q-Noise 100% sound / 88,5% coverage, G-Truth không đổi. | 19/10/2026: Google Form thu câu hỏi (đồng ý NĐ 13/2023, mã rút lại, câu tự do trước kịch bản) + Q-Elicit 20 kịch bản đóng băng (báo riêng, không tính); Q-Real vẫn chưa đạt 0/400 — chờ Loi phát form. | P20-4 (A): mất ĐTBCHK vẫn không tin điểm (M2 ≡ F1), hỏi 1 số ĐTBCHK in thay 5–7 HP, nhận khai báo số in (validate_ocr F5–F11); OCR-Noise dev không đổi (M2 0% coverage), mô phỏng trả lời → 5/5 TRUE. Phương án B (số tích lũy) lập kế hoạch riêng. | C12: ý định xếp loại tốt nghiệp (QD-15 đúng hạng; E29–E37); review phát hiện C15 — KB không hạ bậc (tc_diem_f không sinh, Đ34 k2 b chưa hình thức hoá) → prototype trả UNKNOWN với hạng gốc XS/G; sửa R-Formal lập kế hoạch riêng (ảnh hưởng gold HG). | C15: R-Formal v1.11 — hạ bậc Đ34 k2 a+b (HP điểm cuối F chắc chắn; tc_diem_f, kỷ luật cấp Trường là khai báo; chưa khai báo → mở nhánh), R-F07b; errata G-Truth HG-02/03/04/08; dev chính thức 57/58 (HG-03 từ chối thừa), theo errata 58/58. A17 hỏi HP điều kiện. | C14: kiểm chéo bằng TC tích lũy + ĐTBCTL in sau mỗi học kỳ — cứu học kỳ mất ĐTBCHK khi đủ độ phân giải, luôn kiểm TC tích lũy (bịt lỗ GDTC F→D cho TRUE sai); OCR-Noise dev M2 0/5 → 4/5, Sound 100%. A18: kiểm trên ảnh bảng điểm thật (Windows).</t>
         </is>
       </c>
     </row>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Đọc: không | Code: build_benchmark.py, validate_benchmark.py, run_cpa2.py, baseline.py, nhap_qreal.py | Test: validate_benchmark B1–B11 ĐẠT | Artifact: Tuan20_Benchmark.md, gtruth.json, ocr_noise.json | Lỗi/phát hiện: P20-1 hạng TN mốc nguyên; P20-2 ngoài phạm vi → tot_nghiep; P20-3 đăng ký niên luận; P20-4 OCR M2 từ chối thừa; Q-Real 0/400 chưa đạt | Sửa: P20-1 (v1.10, QD-14), P20-2, P20-3 — rformal C42–C46, integration E10–E16 | Q-Noise: P20-5 parser không dấu → đã sửa, integration E17–E28 | P20-4: w15 F5–F11 | C12: integration E29–E37, QD-15 | C15: rformal C47–C53, graduation D1–D4, student_facts L5, integration E42</t>
+          <t>Đọc: không | Code: build_benchmark.py, validate_benchmark.py, run_cpa2.py, baseline.py, nhap_qreal.py | Test: validate_benchmark B1–B11 ĐẠT | Artifact: Tuan20_Benchmark.md, gtruth.json, ocr_noise.json | Lỗi/phát hiện: P20-1 hạng TN mốc nguyên; P20-2 ngoài phạm vi → tot_nghiep; P20-3 đăng ký niên luận; P20-4 OCR M2 từ chối thừa; Q-Real 0/400 chưa đạt | Sửa: P20-1 (v1.10, QD-14), P20-2, P20-3 — rformal C42–C46, integration E10–E16 | Q-Noise: P20-5 parser không dấu → đã sửa, integration E17–E28 | P20-4: w15 F5–F11 | C12: integration E29–E37, QD-15 | C15: rformal C47–C53, graduation D1–D4, student_facts L5, integration E42 | C14: w15 G0–G15 + G11 ảnh (G9/G12/G13/G15 fail trước sửa)</t>
         </is>
       </c>
     </row>

--- a/Ke_hoach_nghien_cuu_CPA2_24_tuan.xlsx
+++ b/Ke_hoach_nghien_cuu_CPA2_24_tuan.xlsx
@@ -2000,10 +2000,14 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr"/>
+          <t>Đang làm</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Đường ống baseline xong (w21_baseline/: b1 LLM thuần, b2 RAG thuần, b3 tool-calling; OpenAI+Gemini qua urllib; chấm bằng bộ chấm CPA²; validate_baseline 148 kiểm tra, client giả + máy chủ cục bộ). CHƯA chạy thật: thiếu khoá/model/giá (A19). KHÔNG có bảng kết quả → tiêu chí chưa đạt. Review 2 lượt: sửa đốt tiền khi sai model, lộ khoá trong lỗi, trần ngân sách bị bỏ qua, hash đóng băng thiếu; phát hiện corpus.jsonl lỗi thời từ C15 (thiếu R-F07b) — đã sinh lại. 29/78 ca dev có câu hỏi không rõ nghĩa cho baseline (A20) → báo thêm dòng [cau_hoi_ro]. Adapter chưa kiểm API thật (C16).</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -3018,25 +3022,29 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr"/>
+          <t>☑</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Đọc: không | Code: llm.py, baselines.py, run_baseline.py | Test: validate_baseline.py (148) | Artifact: CHƯA có bảng kết quả (chờ khoá API) | Lỗi: câu hỏi không rõ nghĩa 29/78 dev (A20); corpus.jsonl lỗi thời sau C15</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
